--- a/TESTS/zlit_5_snihova_koroleva.xlsx
+++ b/TESTS/zlit_5_snihova_koroleva.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ганс Крістіан Андерсен — великий данський казкар</t>
+          <t>Ганс Крістіан Андерсен</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -622,7 +632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Авторська літературна казка — написана Андерсеном а не записана з народних уст</t>
+          <t>Авторська літературна казка</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -664,7 +679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Данія — Андерсен є найвідомішим датським письменником</t>
+          <t>Данія</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -685,6 +700,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -706,7 +726,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Кай і Герда — хлопчик і дівчинка які дружили змалечку</t>
+          <t>Кай і Герда</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,6 +747,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -748,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Герда — маленька дівчинка що долала всі перешкоди заради порятунку друга Кая</t>
+          <t>Герда</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -769,6 +794,11 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Головна героїня — вона рятує Кая з полону Снігової королеви силою любові і відданості</t>
+          <t>Головна героїня</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -855,6 +890,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -874,7 +914,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Воно показувало все прекрасне потворним — його уламки потрапляли в серця людей і робили їх холодними і злими</t>
+          <t>Воно показувало все прекрасне потворним</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -895,6 +935,11 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -916,7 +961,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Серце перетворюється на лід — людина стає холодною злою і глузливою</t>
+          <t>Серце перетворюється на лід</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,6 +982,11 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Хто створив чарівне дзеркало, яке спотворювало все прекрасне?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Снігова королева</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Злий троль, найгірший з усіх</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Старий чарівник</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Сама природа</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Що сталося з дзеркалом тролів, коли його несли показати небесам?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Його сховали назавжди</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Воно випало і розбилось на мільйони крихітних, майже невидимих скалок</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Його продали</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Воно само зникло</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Що могло статися з людиною, якій скалка дзеркала потрапляла в око чи серце?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічого не відбувалось</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вона починала бачити лише погане у всьому, а серце ставало холодним, як лід</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вона засинала навіки</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вона ставала невидимою</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Якими були стосунки Кая і Герди до того, як скалки дзеркала потрапили Каю в око й серце?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вони ворогували</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вони були найкращими друзями, що разом гралися й вирощували троянди</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вони не знались</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вони були родичами</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Що Кай побачив у візерунках снігу, коли в нього потрапила скалка дзеркала?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічого особливого</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Раптом сніжинки здались йому красивішими за живі квіти, а троянди — бридкими</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він злякався снігу</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він захотів стати художником</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Як Кай почав ставитися до Герди після того, як скалки потрапили йому в око і серце?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він став ще ласкавішим</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він почав насміхатися й кепкувати з неї, чого раніше не робив</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він не помітив змін</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він почав її захищати ще більше</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Куди Кай прив'язав свого санчата того зимового дня, коли зник?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>До дерева</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>До великих білих санок, не знаючи, що в них сидить Снігова королева</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>До паркану</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>До коня</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Що сталося, коли санки зі Снігового королевою рвонули з місця разом із Каєм?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Кай одразу відв'язався</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Санки помчали так швидко, що Кай злякався, але не міг ні крикнути, ні відв'язатись</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Кай зрадів пригоді</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Нічого не сталось, санки зупинились</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Що Снігова королева зробила з Каєм, коли він опинився поруч із нею?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Прогнала його</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Поцілувала його — і він забув про дім, Герду й рідних, а холод перестав йому шкодити</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Подарувала йому подарунки</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Зробила його своїм слугою-в'язнем</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Що Герда зробила навесні, коли всі вважали Кая загиблим?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Залишилась дома сумувати</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вирушила сама шукати Кая, попри небезпеку, віддавши свої червоні черевички річці</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Покликала поліцію</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Чекала, поки Кай повернеться сам</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Хто першим затримав Герду на її шляху, заколисавши квітами в своєму саду?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Розбійники</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Стара жінка-чарівниця, яка хотіла залишити Герду собі назавжди</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Снігова королева</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Ворон</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Як Герда зрозуміла, що має йти далі, і не залишилась у саду чарівниці?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Чарівниця сама її прогнала</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Побачивши троянду, Герда згадала про Кая і заплакала, прогнавши чари забуття</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Прийшли її батьки</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Сад зник раптово</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Хто допоміг Герді потрапити до палацу, де, можливо, перебував Кай?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Стара чарівниця</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Ручний ворон, що розповів про схожого на Кая юнака при дворі</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Розбійники</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Снігова королева сама</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Ким виявився юнак у палаці, схожий на Кая, якого Герда там зустріла?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Це й був Кай</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Це був принц, а не Кай — Герда розчарувалась, але принц і принцеса допомогли їй</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Це був злий чарівник</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Це був сам ворон у людській подобі</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Чим принц і принцеса допомогли Герді продовжити пошуки?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічим не допомогли</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Дали їй теплий одяг, золоту карету і слуг для подальшої подорожі</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Замкнули її в палаці</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Відправили її додому</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>Що сталося з Гердою та її золотою каретою в лісі?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічого, вона проїхала спокійно</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Карету з Гердою захопили розбійники, а саму Герду забрала собі маленька розбійниця</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Карета зламалась</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Герда сама покинула карету</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Хто допоміг Герді дізнатися, де саме перебуває Снігова королева?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Сама маленька розбійниця</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Олень, з яким маленька розбійниця дозволила Герді поїхати на північ</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Ворон</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Принц</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Чому маленька розбійниця, попри грубу поведінку, зрештою відпустила Герду далі?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Її змусили батьки</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Зворушена відданістю Герди Каю, вона допомогла їй, хоч і грубувато</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вона побоялась покарання</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Олень утік сам разом із Гердою</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Хто допомагав Герді й оленю в найхолодніших, найпівнічніших краях на шляху до палацу Снігової королеви?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Розбійники</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Стара лапландка і фінландка — жінки, що знали шлях і силу Герди</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Принц і принцеса</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Сама Снігова королева</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>У чому, за словами фінландки, полягала справжня сила Герди, якої не мала навіть Снігова королева?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>У магії</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>У чистому, люблячому серці дитини, яке сильніше за будь-які чари</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>У зброї</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>У багатстві</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Що сталося з льодяним серцем Кая, коли Герда нарешті знайшла його і заплакала від радості?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічого не сталось</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Її гарячі сльози розтопили скалку в його серці, і Кай теж заплакав, впізнавши Герду</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Кай не впізнав Герду</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Снігова королева забрала Кая ще далі</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>А</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Що символізує Снігова королева у казці?</t>
+          <t>Снігова королева символізує холод, байдужість і відчуження, що оволодівають серцем людини.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,21 +2133,19 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Що символізує образ Герди?</t>
+          <t>Образ Герди символізує силу любові, відданості й чистого серця, здатного перебороти будь-яке зло.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>А</t>
@@ -1989,6 +2154,11 @@
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,29 +2170,32 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Яке значення мають сльози Герди у фіналі казки?</t>
+          <t>Сльози Герди у фіналі казки не мають жодного значення для сюжету.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Яким чином Герда врятувала Кая від чар Снігової королеви?</t>
+          <t>Герда врятувала Кая, гарячими слізьми розтопивши скалку льоду в його серці.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,29 +2244,32 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Які перешкоди долала Герда на шляху до Кая?</t>
+          <t>На шляху до Кая Герда долала перешкоди сама, без жодної допомоги.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,21 +2281,19 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Яка головна ідея казки «Снігова королева»?</t>
+          <t>Головна ідея казки — любов і відданість сильніші за холод і байдужість.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>А</t>
@@ -2125,6 +2302,11 @@
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,27 +2412,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які перешкоди долала Герда рятуючи Кая?</t>
+          <t>Хто допомагав Герді на шляху до Кая?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Зустріч зі старою чарівницею</t>
+          <t>Ручний ворон</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Полон у розбійниці</t>
+          <t>Маленька розбійниця та олень</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Бездоріжжя і снігові заметілі</t>
+          <t>Снігова королева</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Подорож на північ до крижаного палацу</t>
+          <t>Лапландка і фінландка</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2251,6 +2443,11 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2469,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Снігова королева — забрала його на крижаний Північ у свій крижаний палац</t>
+          <t>Снігова королева</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2293,6 +2490,11 @@
       <c r="H44" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2516,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>У крижаному палаці Снігової королеви — складав з льодяних уламків слово «Вічність» але не міг</t>
+          <t>У крижаному палаці Снігової королеви</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2335,6 +2537,11 @@
       <c r="H45" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Слово «Вічність» — якби він склав його Снігова королева дала б йому весь світ і нові ковзани</t>
+          <t>Слово «Вічність»</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
